--- a/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/расчеты Останкино ЗПФ/дв 03,08,26 днрсч ост зпф.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/расчеты Останкино ЗПФ/дв 03,08,26 днрсч ост зпф.xlsx
@@ -1,26 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\расчеты Останкино ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDAE755C-D279-488B-8CA8-7159EE02D693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D6881F-67EA-464A-BD16-03A4447941CC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="44">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -68,9 +76,6 @@
   </si>
   <si>
     <t>ср нов</t>
-  </si>
-  <si>
-    <t>расчет</t>
   </si>
   <si>
     <t>кон ост</t>
@@ -149,6 +154,12 @@
   </si>
   <si>
     <t>7216 СОЧНЫЕ СО СЛ.МАСЛ.ПМ пельм пл.0.7кг зам. ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>заказ</t>
+  </si>
+  <si>
+    <t>10,08,</t>
   </si>
 </sst>
 </file>
@@ -736,34 +747,34 @@
         <v>15</v>
       </c>
       <c r="Q3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="U3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y3" s="2" t="s">
+      <c r="Z3" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="AA3" s="1"/>
       <c r="AB3" s="1"/>
@@ -805,28 +816,30 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q4" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="W4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="X4" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
@@ -897,7 +910,7 @@
       </c>
       <c r="Q5" s="4">
         <f t="shared" si="0"/>
-        <v>502</v>
+        <v>520</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
@@ -924,7 +937,7 @@
       <c r="Y5" s="1"/>
       <c r="Z5" s="4">
         <f>SUM(Z6:Z500)</f>
-        <v>160.35</v>
+        <v>166</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
@@ -952,10 +965,10 @@
     </row>
     <row r="6" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="C6" s="1">
         <v>133</v>
@@ -976,7 +989,7 @@
         <v>120</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1">
@@ -1018,10 +1031,10 @@
         <v>1</v>
       </c>
       <c r="Y6" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Z6" s="1">
-        <f>G6*Q6</f>
+        <f t="shared" ref="Z6:Z16" si="2">G6*Q6</f>
         <v>0</v>
       </c>
       <c r="AA6" s="1"/>
@@ -1050,10 +1063,10 @@
     </row>
     <row r="7" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="C7" s="1">
         <v>41.228999999999999</v>
@@ -1072,7 +1085,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1">
@@ -1086,16 +1099,16 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1">
-        <f t="shared" ref="P7:P16" si="2">E7/5</f>
+        <f t="shared" ref="P7:P16" si="3">E7/5</f>
         <v>1.8348</v>
       </c>
       <c r="Q7" s="5"/>
       <c r="R7" s="1">
-        <f t="shared" ref="R7:R16" si="3">(F7+O7+Q7)/P7</f>
+        <f t="shared" ref="R7:R16" si="4">(F7+O7+Q7)/P7</f>
         <v>14.966753869631567</v>
       </c>
       <c r="S7" s="1">
-        <f t="shared" ref="S7:S16" si="4">(F7+O7)/P7</f>
+        <f t="shared" ref="S7:S16" si="5">(F7+O7)/P7</f>
         <v>14.966753869631567</v>
       </c>
       <c r="T7" s="1">
@@ -1115,7 +1128,7 @@
       </c>
       <c r="Y7" s="1"/>
       <c r="Z7" s="1">
-        <f>G7*Q7</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA7" s="1"/>
@@ -1144,10 +1157,10 @@
     </row>
     <row r="8" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" s="1">
         <v>95.638000000000005</v>
@@ -1166,7 +1179,7 @@
         <v>120</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1">
@@ -1180,18 +1193,18 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.8155999999999999</v>
       </c>
       <c r="Q8" s="5"/>
       <c r="R8" s="1">
-        <f t="shared" si="3"/>
-        <v>47.675699493280462</v>
-      </c>
-      <c r="S8" s="1">
         <f t="shared" si="4"/>
         <v>47.675699493280462</v>
       </c>
+      <c r="S8" s="1">
+        <f t="shared" si="5"/>
+        <v>47.675699493280462</v>
+      </c>
       <c r="T8" s="1">
         <v>0.90480000000000005</v>
       </c>
@@ -1208,10 +1221,10 @@
         <v>0.90839999999999999</v>
       </c>
       <c r="Y8" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Z8" s="1">
-        <f>G8*Q8</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA8" s="1"/>
@@ -1240,10 +1253,10 @@
     </row>
     <row r="9" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" s="1">
         <v>175</v>
@@ -1262,7 +1275,7 @@
         <v>120</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1">
@@ -1276,18 +1289,18 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.4</v>
       </c>
       <c r="Q9" s="5"/>
       <c r="R9" s="1">
-        <f t="shared" si="3"/>
-        <v>65.416666666666671</v>
-      </c>
-      <c r="S9" s="1">
         <f t="shared" si="4"/>
         <v>65.416666666666671</v>
       </c>
+      <c r="S9" s="1">
+        <f t="shared" si="5"/>
+        <v>65.416666666666671</v>
+      </c>
       <c r="T9" s="1">
         <v>0.4</v>
       </c>
@@ -1304,10 +1317,10 @@
         <v>2.4</v>
       </c>
       <c r="Y9" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Z9" s="1">
-        <f>G9*Q9</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA9" s="1"/>
@@ -1336,10 +1349,10 @@
     </row>
     <row r="10" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1">
         <v>76</v>
@@ -1360,7 +1373,7 @@
         <v>120</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1">
@@ -1376,19 +1389,18 @@
         <v>50</v>
       </c>
       <c r="P10" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="Q10" s="5">
-        <f t="shared" ref="Q7:Q16" si="5">15*P10-O10-F10</f>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="R10" s="1">
-        <f t="shared" si="3"/>
-        <v>15</v>
+        <f t="shared" si="4"/>
+        <v>15.857142857142858</v>
       </c>
       <c r="S10" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
       <c r="T10" s="1">
@@ -1408,8 +1420,8 @@
       </c>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1">
-        <f>G10*Q10</f>
-        <v>4.2</v>
+        <f t="shared" si="2"/>
+        <v>6</v>
       </c>
       <c r="AA10" s="1"/>
       <c r="AB10" s="1"/>
@@ -1437,10 +1449,10 @@
     </row>
     <row r="11" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" s="1">
         <v>200</v>
@@ -1461,7 +1473,7 @@
         <v>120</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1">
@@ -1475,19 +1487,18 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>22.8</v>
       </c>
       <c r="Q11" s="5">
+        <v>270</v>
+      </c>
+      <c r="R11" s="1">
+        <f t="shared" si="4"/>
+        <v>15.263157894736842</v>
+      </c>
+      <c r="S11" s="1">
         <f t="shared" si="5"/>
-        <v>264</v>
-      </c>
-      <c r="R11" s="1">
-        <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
-      <c r="S11" s="1">
-        <f t="shared" si="4"/>
         <v>3.4210526315789473</v>
       </c>
       <c r="T11" s="1">
@@ -1507,8 +1518,8 @@
       </c>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1">
-        <f>G11*Q11</f>
-        <v>79.2</v>
+        <f t="shared" si="2"/>
+        <v>81</v>
       </c>
       <c r="AA11" s="1"/>
       <c r="AB11" s="1"/>
@@ -1536,10 +1547,10 @@
     </row>
     <row r="12" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="1">
         <v>112</v>
@@ -1560,7 +1571,7 @@
         <v>120</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1">
@@ -1576,19 +1587,18 @@
         <v>10</v>
       </c>
       <c r="P12" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>12.4</v>
       </c>
       <c r="Q12" s="5">
+        <v>130</v>
+      </c>
+      <c r="R12" s="1">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="S12" s="1">
         <f t="shared" si="5"/>
-        <v>130</v>
-      </c>
-      <c r="R12" s="1">
-        <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
-      <c r="S12" s="1">
-        <f t="shared" si="4"/>
         <v>4.5161290322580641</v>
       </c>
       <c r="T12" s="1">
@@ -1608,7 +1618,7 @@
       </c>
       <c r="Y12" s="1"/>
       <c r="Z12" s="1">
-        <f>G12*Q12</f>
+        <f t="shared" si="2"/>
         <v>45.5</v>
       </c>
       <c r="AA12" s="1"/>
@@ -1637,10 +1647,10 @@
     </row>
     <row r="13" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C13" s="1">
         <v>95</v>
@@ -1661,7 +1671,7 @@
         <v>120</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1">
@@ -1677,19 +1687,18 @@
         <v>110</v>
       </c>
       <c r="P13" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>11.2</v>
       </c>
       <c r="Q13" s="5">
+        <v>30</v>
+      </c>
+      <c r="R13" s="1">
+        <f t="shared" si="4"/>
+        <v>15.089285714285715</v>
+      </c>
+      <c r="S13" s="1">
         <f t="shared" si="5"/>
-        <v>29</v>
-      </c>
-      <c r="R13" s="1">
-        <f t="shared" si="3"/>
-        <v>15.000000000000002</v>
-      </c>
-      <c r="S13" s="1">
-        <f t="shared" si="4"/>
         <v>12.410714285714286</v>
       </c>
       <c r="T13" s="1">
@@ -1709,8 +1718,8 @@
       </c>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1">
-        <f>G13*Q13</f>
-        <v>8.6999999999999993</v>
+        <f t="shared" si="2"/>
+        <v>9</v>
       </c>
       <c r="AA13" s="1"/>
       <c r="AB13" s="1"/>
@@ -1738,10 +1747,10 @@
     </row>
     <row r="14" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C14" s="1">
         <v>98</v>
@@ -1762,7 +1771,7 @@
         <v>120</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1">
@@ -1778,19 +1787,18 @@
         <v>30</v>
       </c>
       <c r="P14" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>11.6</v>
       </c>
       <c r="Q14" s="5">
+        <v>70</v>
+      </c>
+      <c r="R14" s="1">
+        <f t="shared" si="4"/>
+        <v>15.431034482758621</v>
+      </c>
+      <c r="S14" s="1">
         <f t="shared" si="5"/>
-        <v>65</v>
-      </c>
-      <c r="R14" s="1">
-        <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
-      <c r="S14" s="1">
-        <f t="shared" si="4"/>
         <v>9.3965517241379306</v>
       </c>
       <c r="T14" s="1">
@@ -1810,8 +1818,8 @@
       </c>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1">
-        <f>G14*Q14</f>
-        <v>22.75</v>
+        <f t="shared" si="2"/>
+        <v>24.5</v>
       </c>
       <c r="AA14" s="1"/>
       <c r="AB14" s="1"/>
@@ -1839,10 +1847,10 @@
     </row>
     <row r="15" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C15" s="1">
         <v>188</v>
@@ -1859,7 +1867,7 @@
         <v>120</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -1871,18 +1879,18 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q15" s="5"/>
       <c r="R15" s="1" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S15" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="S15" s="1" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="T15" s="1">
         <v>0.4</v>
       </c>
@@ -1899,10 +1907,10 @@
         <v>1.6</v>
       </c>
       <c r="Y15" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Z15" s="1">
-        <f>G15*Q15</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA15" s="1"/>
@@ -1931,10 +1939,10 @@
     </row>
     <row r="16" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C16" s="1">
         <v>244</v>
@@ -1955,7 +1963,7 @@
         <v>180</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1">
@@ -1969,18 +1977,18 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.6</v>
       </c>
       <c r="Q16" s="5"/>
       <c r="R16" s="1">
-        <f t="shared" si="3"/>
-        <v>39.473684210526315</v>
-      </c>
-      <c r="S16" s="1">
         <f t="shared" si="4"/>
         <v>39.473684210526315</v>
       </c>
+      <c r="S16" s="1">
+        <f t="shared" si="5"/>
+        <v>39.473684210526315</v>
+      </c>
       <c r="T16" s="1">
         <v>8.4</v>
       </c>
@@ -1997,10 +2005,10 @@
         <v>6.2</v>
       </c>
       <c r="Y16" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Z16" s="1">
-        <f>G16*Q16</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AA16" s="1"/>
